--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/01_CHUAN_IMPORT_QUIZIZZ_QUIZ_COM_904_CAU/Day_13_Monitoring, Logging _ Observability/Day_13_Phan_01_19_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/01_CHUAN_IMPORT_QUIZIZZ_QUIZ_COM_904_CAU/Day_13_Monitoring, Logging _ Observability/Day_13_Phan_01_19_Cau.xlsx
@@ -1167,7 +1167,7 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>9.56</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
@@ -1195,7 +1195,7 @@
       <c r="J14" s="3" t="n"/>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>P=1−(1−0,01)^10=1−0,99^10≈9,56%.</t>
+          <t>Xác suất gặp ít nhất một lượt latency &gt; 5s trong 10 lượt chat độc lập: P = 1 - (1 - 0,01)^10 = 1 - 0,99^10 ≈ 0,0956178... = 9,56%.</t>
         </is>
       </c>
     </row>
@@ -1343,7 +1343,7 @@
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,2,3</t>
         </is>
       </c>
       <c r="I17" s="4" t="n">
@@ -1352,7 +1352,7 @@
       <c r="J17" s="3" t="n"/>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Chọn signal thực sự so output với evidence hoặc authority.</t>
+          <t>Đánh giá rủi ro hallucination khi dữ liệu lớn đòi hỏi phối hợp đa tầng: (a) Kiểm tra đối chiếu tự động giữa thực thể/claim với nguồn truy xuất (groundedness check), (b) lấy mẫu định kỳ chấm bằng LLM judge có version cố định, (c) chuyển chuyên gia con người hoặc hệ thống hồ sơ gốc (system-of-record) rà soát các trường hợp bất đồng có rủi ro cao.</t>
         </is>
       </c>
     </row>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="G18" s="3" t="n"/>
       <c r="H18" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I18" s="4" t="n">
         <v>60</v>
@@ -1400,7 +1400,7 @@
       <c r="J18" s="3" t="n"/>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Đối chiếu các lựa chọn với: Tool success rate, Timeout rate.</t>
+          <t>Báo cáo số liệu công cụ chính xác: Tỷ lệ thành công là 80/100 = 80%; các tỷ lệ lỗi (timeout, invalid schema, provider failure) và tỷ lệ lặp lại (loop rate) phải được tính toán dựa trên đúng mẫu số tương ứng.</t>
         </is>
       </c>
     </row>
